--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104572_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104572_W13.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3211</v>
+        <v>4.1411</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6972</v>
+        <v>5.4217</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.3761</v>
+        <v>-1.2806</v>
       </c>
       <c r="G2" t="n">
-        <v>2.6771</v>
+        <v>2.6741</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7259</v>
+        <v>0.7212</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9512</v>
+        <v>1.953</v>
       </c>
       <c r="J2" t="n">
-        <v>5.9545</v>
+        <v>5.9249</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0016</v>
+        <v>1.9855</v>
       </c>
       <c r="L2" t="n">
-        <v>3.9529</v>
+        <v>3.9394</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.2774</v>
+        <v>-3.2508</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2758</v>
+        <v>-1.2643</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.793</v>
+        <v>-0.9688</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5353</v>
+        <v>-0.7716</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2577</v>
+        <v>-0.1972</v>
       </c>
       <c r="V2" t="n">
-        <v>1.5297</v>
+        <v>1.5253</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0983</v>
+        <v>0.1637</v>
       </c>
       <c r="E3" t="n">
-        <v>1.974</v>
+        <v>2.3581</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.0723</v>
+        <v>-2.1944</v>
       </c>
       <c r="G3" t="n">
-        <v>0.261</v>
+        <v>0.2487</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1601</v>
+        <v>-0.1635</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4211</v>
+        <v>0.4122</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2957</v>
+        <v>3.2575</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7765</v>
+        <v>1.7614</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5192</v>
+        <v>1.496</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.0347</v>
+        <v>-3.0087</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.9366</v>
+        <v>-1.9249</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.7617</v>
+        <v>-1.4995</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3217</v>
+        <v>-0.8993</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4401</v>
+        <v>-0.6002</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. BAGAYOKO</t>
+          <t>S. LAZAREVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.9802</v>
+        <v>-2.384</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3986</v>
+        <v>-1.5156</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3788</v>
+        <v>-0.8683999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.281</v>
+        <v>-2.5975</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.8657</v>
+        <v>-0.9308</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4153</v>
+        <v>-1.6667</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4271</v>
+        <v>-1.4386</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4644</v>
+        <v>-0.6862</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0373</v>
+        <v>-0.7524</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.8539</v>
+        <v>-1.1588</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4012</v>
+        <v>-0.2446</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.4526</v>
+        <v>-0.9143</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1024</v>
+        <v>0.3924</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8257</v>
+        <v>-0.077</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2767</v>
+        <v>0.4694</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4822</v>
+        <v>-1.0895</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.4822</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. LAZAREVIC</t>
+          <t>B. BAGAYOKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.4783</v>
+        <v>-2.8758</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4617</v>
+        <v>-0.3672</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0166</v>
+        <v>-2.5086</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.6064</v>
+        <v>-3.2768</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9351</v>
+        <v>-1.8695</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6712</v>
+        <v>-1.4073</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4315</v>
+        <v>-0.4389</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6825</v>
+        <v>-0.4761</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.749</v>
+        <v>0.0372</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1749</v>
+        <v>-2.838</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2526</v>
+        <v>-1.3934</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9222</v>
+        <v>-1.4446</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9073</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3133</v>
+        <v>0.1914</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0302</v>
+        <v>0.0717</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3436</v>
+        <v>0.1198</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.1965</v>
+        <v>-2.9569</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5295</v>
+        <v>-0.2562</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.6671</v>
+        <v>-2.7007</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.5337</v>
+        <v>-3.5329</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0247</v>
+        <v>0.0149</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.5584</v>
+        <v>-3.5478</v>
       </c>
       <c r="J6" t="n">
-        <v>0.746</v>
+        <v>0.722</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4577</v>
+        <v>1.4372</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7117</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.2797</v>
+        <v>-4.2549</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.8467</v>
+        <v>-2.8326</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9823</v>
+        <v>-0.7411</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.234</v>
+        <v>-0.9295</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2516</v>
+        <v>0.1884</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.5298</v>
+        <v>-3.6212</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5664</v>
+        <v>-1.811</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9634</v>
+        <v>-1.8101</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8365</v>
+        <v>-1.8294</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2265</v>
+        <v>-0.2269</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.6099</v>
+        <v>-1.6025</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9555</v>
+        <v>0.9373</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7419</v>
+        <v>1.7269</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.792</v>
+        <v>-2.7667</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9684</v>
+        <v>-1.9538</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5426</v>
+        <v>-0.6342</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1875</v>
+        <v>-0.4021</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3551</v>
+        <v>-0.232</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4371</v>
+        <v>0.4358</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2763</v>
+        <v>0.278</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.5589</v>
+        <v>-3.7446</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0144</v>
+        <v>-2.3215</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5445</v>
+        <v>-1.4232</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3796</v>
+        <v>-3.374</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.4068</v>
+        <v>-2.4122</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9728</v>
+        <v>-0.9618</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.923</v>
+        <v>-0.9389</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1469</v>
+        <v>-1.1623</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2239</v>
+        <v>0.2234</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4566</v>
+        <v>-2.4351</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2599</v>
+        <v>-1.2499</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1967</v>
+        <v>-1.1852</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8598</v>
+        <v>-1.0535</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1179</v>
+        <v>-0.4021</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7419</v>
+        <v>-0.6513</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.1379</v>
+        <v>-5.3726</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2416</v>
+        <v>-1.7298</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.8963</v>
+        <v>-3.6428</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.5487</v>
+        <v>-3.5458</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2323</v>
+        <v>-1.2294</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3163</v>
+        <v>-2.3164</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.9515</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7202</v>
+        <v>0.71</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6501</v>
+        <v>-1.6614</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.6188</v>
+        <v>-2.5943</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.9525</v>
+        <v>-1.9394</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.6663</v>
+        <v>-0.6549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.6141</v>
+        <v>-0.8561</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0434</v>
+        <v>-0.5021</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5707</v>
+        <v>-0.354</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.2946</v>
+        <v>-2.2879</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.585100000000001</v>
+        <v>-8.3094</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6033</v>
+        <v>-6.1135</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9818</v>
+        <v>-2.1958</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.8171</v>
+        <v>-5.8216</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.173</v>
+        <v>-3.1791</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.6442</v>
+        <v>-2.6425</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.3775</v>
+        <v>-2.4116</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3618</v>
+        <v>-1.3832</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.0157</v>
+        <v>-1.0284</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.4397</v>
+        <v>-3.41</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8112</v>
+        <v>-1.7959</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6285</v>
+        <v>-1.6141</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R10" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4584</v>
+        <v>-1.1708</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.3035</v>
+        <v>-0.7623</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1549</v>
+        <v>-0.4085</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0515</v>
+        <v>0.0488</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.1997</v>
+        <v>-9.139799999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6964</v>
+        <v>-4.7207</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.5033</v>
+        <v>-4.4191</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.5692</v>
+        <v>-5.5775</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8427</v>
+        <v>-1.8411</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.7265</v>
+        <v>-3.7364</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.0057</v>
+        <v>-3.0249</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.5484</v>
+        <v>-2.5628</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.5635</v>
+        <v>-2.5526</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3853</v>
+        <v>-1.3789</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.1781</v>
+        <v>-1.1736</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.672</v>
+        <v>-0.611</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5565</v>
+        <v>-0.5576</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1155</v>
+        <v>-0.0534</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.0251</v>
+        <v>-9.6745</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.8182</v>
+        <v>-7.4293</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2069</v>
+        <v>-2.2452</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.9899</v>
+        <v>-6.9953</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2353</v>
+        <v>-0.2273</v>
       </c>
       <c r="I12" t="n">
-        <v>-6.7546</v>
+        <v>-6.7679</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.5065</v>
+        <v>-4.5325</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.8701</v>
+        <v>-4.8945</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4834</v>
+        <v>-2.4628</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.2045</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8166</v>
+        <v>-0.3929</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2516</v>
+        <v>0.1884</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6556</v>
+        <v>-0.6536999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-44.46870000000001</v>
+        <v>-43.774</v>
       </c>
       <c r="E13" t="n">
-        <v>-18.8617</v>
+        <v>-18.485</v>
       </c>
       <c r="F13" t="n">
-        <v>-25.6071</v>
+        <v>-25.2889</v>
       </c>
       <c r="G13" t="n">
-        <v>-33.624</v>
+        <v>-33.628</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.3269</v>
+        <v>-11.3437</v>
       </c>
       <c r="I13" t="n">
-        <v>-22.2969</v>
+        <v>-22.2841</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.6495</v>
+        <v>-2.895200000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9487</v>
+        <v>3.8131</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.598099999999999</v>
+        <v>-6.708300000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-30.9746</v>
+        <v>-30.7327</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.2755</v>
+        <v>-15.1567</v>
       </c>
       <c r="O13" t="n">
-        <v>-15.6989</v>
+        <v>-15.5759</v>
       </c>
       <c r="P13" t="n">
-        <v>1.134099999999999</v>
+        <v>1.137999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7443</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8782</v>
+        <v>15.9341</v>
       </c>
       <c r="S13" t="n">
-        <v>-7.8332</v>
+        <v>-7.1557</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.320900000000001</v>
+        <v>-5.6248</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5124</v>
+        <v>-1.5306</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.145799999999999</v>
+        <v>-4.128699999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>4.8529</v>
+        <v>4.8313</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.998799999999999</v>
+        <v>-8.960000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.4208</v>
+        <v>8.0418</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5264</v>
+        <v>6.8339</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8944</v>
+        <v>1.2079</v>
       </c>
       <c r="G14" t="n">
-        <v>3.67</v>
+        <v>3.6538</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3895</v>
+        <v>-0.396</v>
       </c>
       <c r="I14" t="n">
-        <v>4.0595</v>
+        <v>4.0498</v>
       </c>
       <c r="J14" t="n">
-        <v>4.8098</v>
+        <v>4.769</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.0733</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>4.8831</v>
+        <v>4.8627</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1398</v>
+        <v>-1.1152</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3162</v>
+        <v>-0.3023</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2492</v>
+        <v>0.388</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4688</v>
+        <v>-0.1141</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2196</v>
+        <v>0.5021</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.1179</v>
+        <v>6.3647</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3219</v>
+        <v>5.4794</v>
       </c>
       <c r="F15" t="n">
-        <v>0.796</v>
+        <v>0.8853</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9719</v>
+        <v>1.9836</v>
       </c>
       <c r="H15" t="n">
-        <v>0.186</v>
+        <v>0.1975</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7859</v>
+        <v>1.7861</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2726</v>
+        <v>1.2646</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6992</v>
+        <v>0.719</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6691</v>
+        <v>0.6766</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7339</v>
+        <v>0.9745</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2249</v>
+        <v>0.4016</v>
       </c>
       <c r="U15" t="n">
-        <v>0.509</v>
+        <v>0.5729</v>
       </c>
       <c r="V15" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W15" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3671</v>
+        <v>5.9851</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7458</v>
+        <v>2.5891</v>
       </c>
       <c r="F16" t="n">
-        <v>3.6214</v>
+        <v>3.396</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6214</v>
+        <v>5.6145</v>
       </c>
       <c r="H16" t="n">
-        <v>1.4126</v>
+        <v>1.4158</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2088</v>
+        <v>4.1988</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0772</v>
+        <v>4.0494</v>
       </c>
       <c r="K16" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L16" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5442</v>
+        <v>1.5652</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O16" t="n">
-        <v>1.8286</v>
+        <v>1.8386</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3997</v>
+        <v>1.0338</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2299</v>
+        <v>0.1136</v>
       </c>
       <c r="U16" t="n">
-        <v>1.1698</v>
+        <v>0.9203</v>
       </c>
       <c r="V16" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W16" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.8282</v>
+        <v>4.0735</v>
       </c>
       <c r="E17" t="n">
-        <v>3.7939</v>
+        <v>2.957</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0343</v>
+        <v>1.1165</v>
       </c>
       <c r="G17" t="n">
-        <v>1.3246</v>
+        <v>1.3268</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2237</v>
+        <v>0.2213</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1009</v>
+        <v>1.1055</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7263</v>
+        <v>1.7133</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9799</v>
+        <v>0.9685</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4017</v>
+        <v>-0.3865</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3546</v>
+        <v>0.3608</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>1.8231</v>
+        <v>1.0638</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5213</v>
+        <v>0.699</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3018</v>
+        <v>0.3648</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.3138</v>
+        <v>3.5664</v>
       </c>
       <c r="E18" t="n">
-        <v>1.359</v>
+        <v>0.5194</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9548</v>
+        <v>3.047</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5285</v>
+        <v>2.5407</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0202</v>
+        <v>0.0228</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5083</v>
+        <v>2.5179</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5465</v>
+        <v>1.5347</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6509</v>
+        <v>0.641</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8956</v>
+        <v>0.8937</v>
       </c>
       <c r="M18" t="n">
-        <v>0.982</v>
+        <v>1.006</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O18" t="n">
-        <v>1.6127</v>
+        <v>1.6242</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5585</v>
+        <v>0.7981</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9467</v>
+        <v>0.1228</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6118</v>
+        <v>0.6752</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>3.0906</v>
+        <v>3.2812</v>
       </c>
       <c r="E19" t="n">
-        <v>2.6082</v>
+        <v>2.9322</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4825</v>
+        <v>0.349</v>
       </c>
       <c r="G19" t="n">
-        <v>4.201</v>
+        <v>4.1945</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5484</v>
+        <v>2.5394</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6526</v>
+        <v>1.6551</v>
       </c>
       <c r="J19" t="n">
-        <v>4.315</v>
+        <v>4.2927</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4865</v>
+        <v>2.4681</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.114</v>
+        <v>-0.0982</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.434</v>
+        <v>0.6331</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.6262</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.3176</v>
+        <v>-1.3187</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.916</v>
+        <v>3.1348</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5103</v>
+        <v>0.4199</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4057</v>
+        <v>2.715</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5488</v>
+        <v>1.124</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6319</v>
+        <v>1.0598</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9169</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0387</v>
+        <v>1.0483</v>
       </c>
       <c r="K20" t="n">
-        <v>1.42</v>
+        <v>1.1754</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.3813</v>
+        <v>-0.127</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5102</v>
+        <v>0.0757</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.788</v>
+        <v>-0.1155</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2982</v>
+        <v>0.1912</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1342</v>
+        <v>1.8211</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4352</v>
+        <v>0.4449</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4869</v>
+        <v>0.0136</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9221</v>
+        <v>0.4313</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9320000000000001</v>
+        <v>2.0212</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.6342</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.871</v>
+        <v>3.0292</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6891</v>
+        <v>0.7183</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1819</v>
+        <v>2.3109</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1219</v>
+        <v>1.5503</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0606</v>
+        <v>0.6373</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0613</v>
+        <v>0.913</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0704</v>
+        <v>1.018</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1878</v>
+        <v>1.4134</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1174</v>
+        <v>-0.3954</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0515</v>
+        <v>0.5322</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1272</v>
+        <v>-0.7761</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1787</v>
+        <v>1.3083</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1781</v>
+        <v>0.5473</v>
       </c>
       <c r="T21" t="n">
-        <v>0.248</v>
+        <v>-0.251</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0699</v>
+        <v>0.7983</v>
       </c>
       <c r="V21" t="n">
-        <v>2.0246</v>
+        <v>0.9317</v>
       </c>
       <c r="W21" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.0395</v>
+        <v>2.6034</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.4741</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1342</v>
+        <v>2.1293</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3878</v>
+        <v>0.3862</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5208</v>
+        <v>1.5276</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.1329</v>
+        <v>-1.1414</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3045</v>
+        <v>0.2816</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9871</v>
+        <v>0.9825</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6825</v>
+        <v>-0.7009</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0833</v>
+        <v>0.1046</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2906</v>
+        <v>0.8514</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3992</v>
+        <v>0.1925</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6899</v>
+        <v>0.6589</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.6889</v>
+        <v>1.9905</v>
       </c>
       <c r="E23" t="n">
-        <v>1.7525</v>
+        <v>2.0937</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0636</v>
+        <v>-0.1032</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2668</v>
+        <v>3.2716</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1428</v>
+        <v>0.1463</v>
       </c>
       <c r="I23" t="n">
-        <v>3.124</v>
+        <v>3.1253</v>
       </c>
       <c r="J23" t="n">
-        <v>3.0953</v>
+        <v>3.0857</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2295</v>
+        <v>1.2238</v>
       </c>
       <c r="L23" t="n">
-        <v>1.8658</v>
+        <v>1.8618</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O23" t="n">
-        <v>1.2582</v>
+        <v>1.2634</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2879</v>
+        <v>0.5808</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2087</v>
+        <v>0.1462</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4966</v>
+        <v>0.4345</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9825</v>
+        <v>1.7268</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6185</v>
+        <v>-0.1863</v>
       </c>
       <c r="F24" t="n">
-        <v>1.6011</v>
+        <v>1.9131</v>
       </c>
       <c r="G24" t="n">
-        <v>5.4022</v>
+        <v>5.3958</v>
       </c>
       <c r="H24" t="n">
-        <v>2.6248</v>
+        <v>2.6223</v>
       </c>
       <c r="I24" t="n">
-        <v>2.7774</v>
+        <v>2.7735</v>
       </c>
       <c r="J24" t="n">
-        <v>3.9726</v>
+        <v>3.9465</v>
       </c>
       <c r="K24" t="n">
-        <v>3.0824</v>
+        <v>3.0682</v>
       </c>
       <c r="L24" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4297</v>
+        <v>1.4493</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8873</v>
+        <v>1.8951</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1267</v>
+        <v>0.6284</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4174</v>
+        <v>0.0556</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2906</v>
+        <v>0.5729</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.0246</v>
+        <v>-2.0212</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8323</v>
+        <v>1.4632</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0134</v>
+        <v>0.4582</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8189</v>
+        <v>1.0049</v>
       </c>
       <c r="G25" t="n">
-        <v>2.5789</v>
+        <v>2.5861</v>
       </c>
       <c r="H25" t="n">
-        <v>1.3448</v>
+        <v>1.3496</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2342</v>
+        <v>1.2365</v>
       </c>
       <c r="J25" t="n">
-        <v>3.7455</v>
+        <v>3.7289</v>
       </c>
       <c r="K25" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L25" t="n">
-        <v>2.2736</v>
+        <v>2.2638</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.1666</v>
+        <v>-1.1428</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.0395</v>
+        <v>-1.0273</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S25" t="n">
-        <v>0.068</v>
+        <v>0.6981000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3297</v>
+        <v>0.1438</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3977</v>
+        <v>0.5543</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>44.4686</v>
+        <v>45.2606</v>
       </c>
       <c r="E26" t="n">
-        <v>25.6073</v>
+        <v>25.28890000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>18.8616</v>
+        <v>19.9717</v>
       </c>
       <c r="G26" t="n">
-        <v>33.6238</v>
+        <v>33.6279</v>
       </c>
       <c r="H26" t="n">
-        <v>11.3271</v>
+        <v>11.3437</v>
       </c>
       <c r="I26" t="n">
-        <v>22.2969</v>
+        <v>22.28429999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>30.9744</v>
+        <v>30.7327</v>
       </c>
       <c r="K26" t="n">
-        <v>15.2756</v>
+        <v>15.1566</v>
       </c>
       <c r="L26" t="n">
-        <v>15.6989</v>
+        <v>15.5759</v>
       </c>
       <c r="M26" t="n">
-        <v>2.6495</v>
+        <v>2.8952</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.948700000000001</v>
+        <v>-3.8127</v>
       </c>
       <c r="O26" t="n">
-        <v>6.598000000000001</v>
+        <v>6.708</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.1341</v>
+        <v>-1.1381</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8784</v>
+        <v>-15.9344</v>
       </c>
       <c r="R26" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S26" t="n">
-        <v>7.8331</v>
+        <v>8.642199999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>1.5123</v>
+        <v>1.5304</v>
       </c>
       <c r="U26" t="n">
-        <v>6.3208</v>
+        <v>7.111699999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>4.145799999999999</v>
+        <v>4.128599999999999</v>
       </c>
       <c r="W26" t="n">
-        <v>8.9986</v>
+        <v>8.959900000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-4.8529</v>
+        <v>-4.8312</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104572_W13.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104572_W13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.278</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-2.2879</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.6536999999999999</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-8.960000000000001</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104572_W13.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-4.8312</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
